--- a/output/pdf_financials_xlsx/ADW.A.xlsx
+++ b/output/pdf_financials_xlsx/ADW.A.xlsx
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.737</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>8.525</v>
       </c>
     </row>
     <row r="35">
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.737</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>8.525</v>
       </c>
     </row>
     <row r="37">
@@ -3473,10 +3473,10 @@
         <v>9.239000000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>17.679</v>
+        <v>14.942</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>11.795</v>
+        <v>10.498</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>11.717</v>
@@ -3488,7 +3488,7 @@
         <v>6.904</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>19.063</v>
+        <v>10.538</v>
       </c>
     </row>
     <row r="49">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -46450,7 +46450,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">

--- a/output/pdf_financials_xlsx/ADW.A.xlsx
+++ b/output/pdf_financials_xlsx/ADW.A.xlsx
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>1.488</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -7542,22 +7542,22 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -36134,7 +36134,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E264" s="5" t="n">
         <v>0.003</v>
       </c>

--- a/output/pdf_financials_xlsx/ADW.A.xlsx
+++ b/output/pdf_financials_xlsx/ADW.A.xlsx
@@ -3966,55 +3966,55 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>145.774</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>151.703</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>157.901</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>168.193</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>189.944</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>196.389</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>207.118</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>223.208</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>302.058</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>323.922</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>334.73</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>350.027</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>365.606</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>381.03</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>394.191</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0</v>
+        <v>392.839</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>0</v>
+        <v>401.178</v>
       </c>
     </row>
     <row r="57">
@@ -4027,55 +4027,55 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>60.641</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>66.959</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>73.411</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>79.352</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>84.999</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>91.438</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>98.18899999999999</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>104.37</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>113.867</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>124.173</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>131.297</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>143.107</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>156.591</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>170.765</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>184.059</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>0</v>
+        <v>185.209</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>0</v>
+        <v>196.534</v>
       </c>
     </row>
     <row r="58">
@@ -4097,7 +4097,7 @@
         <v>84.48999999999999</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>88.84099999999999</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>104.945</v>
@@ -4546,31 +4546,31 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>22.211</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>35.392</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>34.25</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>24.796</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>29.667</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>26.964</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>22.615</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>26.151</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>30.133</v>
       </c>
     </row>
     <row r="65">
@@ -4705,55 +4705,55 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>9.119</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>10.599</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>8.654</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>7.802</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>9.657</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>9.702999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>12.045</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>11.194</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>18.608</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>20.444</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>16.294</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>19.214</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>23.967</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>25.115</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>21.722</v>
       </c>
     </row>
     <row r="68">
@@ -4918,25 +4918,25 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>3.018</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>3.826</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>4.523</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>16.56</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>13.411</v>
       </c>
     </row>
     <row r="71">
@@ -4979,25 +4979,25 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>3.018</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>3.826</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>4.523</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>16.56</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>13.411</v>
       </c>
     </row>
     <row r="72">
@@ -5223,25 +5223,25 @@
         <v>51.944</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>76.639</v>
+        <v>73.621</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>8.131</v>
+        <v>4.305</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>7.006</v>
+        <v>2.936</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>12.056</v>
+        <v>7.533</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>10.408</v>
+        <v>5.038</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>12.359</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>12.296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5532,25 +5532,25 @@
         <v>0.4967816963506013</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.4363338668882345</v>
+        <v>0.4486259943060324</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.6572330122677672</v>
+        <v>0.6716395430275555</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.7236785091239295</v>
+        <v>0.7390137942208206</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.8204172876304023</v>
+        <v>0.8382497890694612</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.8627260941777772</v>
+        <v>0.8849679212382526</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.7395705999622614</v>
+        <v>0.8075001435708953</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>0.5573512439693501</v>
+        <v>0.6080976255794154</v>
       </c>
     </row>
     <row r="81">
@@ -7239,31 +7239,31 @@
         <v>0</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>1.673</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>1.226</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>1.876</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>1.399</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>1.483</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.554</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>2.593</v>
       </c>
       <c r="S107" s="3" t="n">
-        <v>0</v>
+        <v>3.165</v>
       </c>
     </row>
     <row r="108">
@@ -7273,10 +7273,10 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0</v>
+        <v>1.247</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -7588,16 +7588,16 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>0</v>
+        <v>-13.665</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0</v>
+        <v>-0.825</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0</v>
+        <v>-0.825</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
@@ -7794,43 +7794,43 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-1.797</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.369</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.822</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.378</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-5.609</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-18.888</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-9.289</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-3.033</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-1.352</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-1.795</v>
       </c>
       <c r="S116" s="3" t="n">
-        <v>0</v>
+        <v>-1.738</v>
       </c>
     </row>
     <row r="117">
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>27.386</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-4.748</v>
+        <v>22.638</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>-22.75</v>
@@ -8605,16 +8605,16 @@
         <v>0</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>0</v>
+        <v>-0.655</v>
       </c>
       <c r="O128" s="3" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="P128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>0</v>
+        <v>-1.177</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0</v>
@@ -10754,7 +10754,11 @@
           <t>Current portion of lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11326,7 +11330,11 @@
           <t>Lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -17340,7 +17348,11 @@
           <t>Lease obligations (note 2)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -28544,7 +28556,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -29620,7 +29636,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -31986,7 +32006,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -32918,7 +32942,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -35618,7 +35646,11 @@
           <t>Deferred financing fees paid (note 11)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -36954,7 +36986,11 @@
           <t>Share based compensation expense</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -42342,7 +42378,11 @@
           <t>Acquisition of businesses</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -43186,7 +43226,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E332" s="5" t="n">
         <v>-2.605</v>
       </c>
@@ -43494,7 +43538,11 @@
           <t>Impairment charges</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E335" s="5" t="n">
         <v>0.148</v>
       </c>
@@ -44122,7 +44170,11 @@
           <t>Acquisition of business</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -45592,7 +45644,11 @@
           <t>Acquisition of businesses (note 2)</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E355" s="5" t="n">
         <v>-13.665</v>
       </c>
@@ -45802,7 +45858,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E357" s="5" t="n">
         <v>27.386</v>
       </c>
